--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92564809402</v>
+        <v>46157.93086102069</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93086102069</v>
+        <v>46157.93164424625</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93164424625</v>
+        <v>46157.93396810155</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93396810155</v>
+        <v>46157.93714420485</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93714420485</v>
+        <v>46158.28213222767</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28213222767</v>
+        <v>46158.29674474976</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29674474976</v>
+        <v>46158.29811191141</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29811191141</v>
+        <v>46158.33384150314</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33384150314</v>
+        <v>46158.36852930914</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36852930914</v>
+        <v>46158.37284285367</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
